--- a/examples/enset/modele-u2.xlsx
+++ b/examples/enset/modele-u2.xlsx
@@ -577,31 +577,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
     <col width="32" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
     <col width="32" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
     <col width="32" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="32" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,105 +613,110 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>nom_prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>departement</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pays_destination</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>duree_jours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>anciennete.annee (qte)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>langues.langue_formation (qte)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>langues.inscription_ceil (qte)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>evaluation_superieur.assiduite</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>evaluation_superieur.competence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>evaluation_superieur.initiative</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evaluation_superieur.disponibilite</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>contribution_1275 (points)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>structures_accompagnement_vie_universitaire.attestation (qte)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>projets_internationaux (points)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>poste_superieur (points)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>penalite_stages_6ans (n manuel)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>montant_indemnite (DA)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>billet_estime (DA)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>frais_divers (DA)</t>
         </is>
@@ -718,13 +724,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$D$2:$D$10</formula1>
     </dataValidation>
   </dataValidations>
